--- a/data/trans_orig/P36B14-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B14-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de refrescos con azúcar en 2016</t>
+          <t>Población según la frecuencia de consumo de refrescos con azúcar en 2016 (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>141419</t>
+          <t>139470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181874</t>
+          <t>181802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>98779</t>
+          <t>99465</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135114</t>
+          <t>137111</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>251961</t>
+          <t>248819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>306408</t>
+          <t>307039</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70205</t>
+          <t>70293</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104694</t>
+          <t>104876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59591</t>
+          <t>57726</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89745</t>
+          <t>88824</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136223</t>
+          <t>140528</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>182691</t>
+          <t>187827</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54086</t>
+          <t>52629</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85833</t>
+          <t>85894</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50718</t>
+          <t>51435</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80781</t>
+          <t>81058</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112766</t>
+          <t>112181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>156736</t>
+          <t>155958</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55510</t>
+          <t>52749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84536</t>
+          <t>85358</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40073</t>
+          <t>40447</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67278</t>
+          <t>66760</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102485</t>
+          <t>103876</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142219</t>
+          <t>144348</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>29347</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52656</t>
+          <t>54582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26816</t>
+          <t>27504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48543</t>
+          <t>50803</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62563</t>
+          <t>62748</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97391</t>
+          <t>95428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116446</t>
+          <t>116956</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154028</t>
+          <t>155784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96755</t>
+          <t>99369</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135354</t>
+          <t>136863</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>226745</t>
+          <t>225217</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>281706</t>
+          <t>279177</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44403</t>
+          <t>45592</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71878</t>
+          <t>72742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62426</t>
+          <t>61883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95301</t>
+          <t>95021</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114332</t>
+          <t>114092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157798</t>
+          <t>156749</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54431</t>
+          <t>56279</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84226</t>
+          <t>87514</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44399</t>
+          <t>44702</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71836</t>
+          <t>74584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107079</t>
+          <t>108505</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>150344</t>
+          <t>150240</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53106</t>
+          <t>52552</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84036</t>
+          <t>81973</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53911</t>
+          <t>53876</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85046</t>
+          <t>83829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115638</t>
+          <t>115223</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158730</t>
+          <t>157144</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35079</t>
+          <t>34322</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62144</t>
+          <t>58512</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39680</t>
+          <t>38255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65299</t>
+          <t>65455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80473</t>
+          <t>78381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116520</t>
+          <t>116265</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>147960</t>
+          <t>151139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193033</t>
+          <t>194238</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49276</t>
+          <t>47704</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76404</t>
+          <t>74110</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>207860</t>
+          <t>206731</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>259970</t>
+          <t>256815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64363</t>
+          <t>63865</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97769</t>
+          <t>95960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21388</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43117</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>91069</t>
+          <t>90499</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130668</t>
+          <t>130215</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76441</t>
+          <t>73412</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111687</t>
+          <t>109072</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>11051</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27808</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>91705</t>
+          <t>92367</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>128615</t>
+          <t>130690</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83794</t>
+          <t>82878</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119327</t>
+          <t>119064</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>24395</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46150</t>
+          <t>46508</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113308</t>
+          <t>114012</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>157245</t>
+          <t>155658</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58383</t>
+          <t>57346</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>89630</t>
+          <t>89230</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14743</t>
+          <t>14535</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33142</t>
+          <t>32656</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78272</t>
+          <t>76943</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114444</t>
+          <t>115648</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>334618</t>
+          <t>333628</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>398054</t>
+          <t>396471</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>227652</t>
+          <t>230911</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>284675</t>
+          <t>287435</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>580350</t>
+          <t>579917</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>664281</t>
+          <t>662089</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>158135</t>
+          <t>160366</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207631</t>
+          <t>212148</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>99637</t>
+          <t>102351</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>141495</t>
+          <t>143055</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>272951</t>
+          <t>269511</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>335731</t>
+          <t>340906</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>194353</t>
+          <t>192448</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>249153</t>
+          <t>247426</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>139569</t>
+          <t>138777</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>185676</t>
+          <t>185603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>345297</t>
+          <t>349325</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>417174</t>
+          <t>417974</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>178437</t>
+          <t>177965</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>229692</t>
+          <t>230410</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128400</t>
+          <t>127908</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>171198</t>
+          <t>173434</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>321210</t>
+          <t>319804</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>388261</t>
+          <t>395115</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>148510</t>
+          <t>146611</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>197877</t>
+          <t>196766</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115909</t>
+          <t>114808</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>159899</t>
+          <t>159213</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278681</t>
+          <t>277734</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>343508</t>
+          <t>343320</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>185890</t>
+          <t>186433</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>232785</t>
+          <t>235102</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>257505</t>
+          <t>261755</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>311650</t>
+          <t>314141</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>462172</t>
+          <t>459952</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>531868</t>
+          <t>529088</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>75948</t>
+          <t>75267</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>110654</t>
+          <t>110783</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>103279</t>
+          <t>103681</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>143783</t>
+          <t>144276</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>189802</t>
+          <t>190688</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>244276</t>
+          <t>243922</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>90391</t>
+          <t>92085</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>131224</t>
+          <t>130078</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>101477</t>
+          <t>100134</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141433</t>
+          <t>139527</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,47 +3734,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
+          <t>18,99%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>230475</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>202978</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>260140</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>15,02%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>19,25%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>230475</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>202115</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>257752</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>17,06%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>14,96%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>88231</t>
+          <t>87542</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>126497</t>
+          <t>127715</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>91492</t>
+          <t>90875</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>131185</t>
+          <t>131826</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>189624</t>
+          <t>189563</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>244467</t>
+          <t>242173</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>82027</t>
+          <t>78808</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>117465</t>
+          <t>116931</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>78825</t>
+          <t>79189</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>115898</t>
+          <t>114965</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>167248</t>
+          <t>169707</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>218343</t>
+          <t>220875</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>16100</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>36592</t>
+          <t>35955</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>422550</t>
+          <t>421151</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>488041</t>
+          <t>487245</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>444804</t>
+          <t>446327</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>518622</t>
+          <t>516982</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>22203</t>
+          <t>23085</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>42884</t>
+          <t>44907</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>140038</t>
+          <t>139358</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>187612</t>
+          <t>185810</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>170439</t>
+          <t>170691</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>225244</t>
+          <t>226018</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>40858</t>
+          <t>41952</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>68321</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>157287</t>
+          <t>157829</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>207413</t>
+          <t>207498</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,47 +4416,47 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
+          <t>19,44%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>235976</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>209493</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>262857</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>17,45%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
           <t>19,43%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>235976</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>210066</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>267620</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>15,53%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>61694</t>
+          <t>62929</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>93763</t>
+          <t>94811</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>123311</t>
+          <t>120161</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>167206</t>
+          <t>166204</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>194085</t>
+          <t>193425</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>249768</t>
+          <t>249161</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>79564</t>
+          <t>80980</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>111569</t>
+          <t>114011</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>104769</t>
+          <t>106268</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>147644</t>
+          <t>147979</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>195483</t>
+          <t>193484</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>249973</t>
+          <t>248266</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1011504</t>
+          <t>1006585</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1117439</t>
+          <t>1118028</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1239630</t>
+          <t>1237415</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1358926</t>
+          <t>1358142</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2276211</t>
+          <t>2285903</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2442212</t>
+          <t>2446052</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>492077</t>
+          <t>490228</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>573960</t>
+          <t>575115</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>541667</t>
+          <t>541495</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>633655</t>
+          <t>628135</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1054172</t>
+          <t>1054863</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1183857</t>
+          <t>1176987</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>571138</t>
+          <t>569976</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>662779</t>
+          <t>663326</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>554624</t>
+          <t>560689</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>651660</t>
+          <t>647227</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1156265</t>
+          <t>1153502</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1283312</t>
+          <t>1287144</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>583392</t>
+          <t>579863</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>674545</t>
+          <t>670113</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>516743</t>
+          <t>514585</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>599957</t>
+          <t>605296</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1126779</t>
+          <t>1120304</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1248416</t>
+          <t>1253355</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>484901</t>
+          <t>485077</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>568277</t>
+          <t>569338</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>427057</t>
+          <t>428719</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>505636</t>
+          <t>508256</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>933784</t>
+          <t>931467</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1052841</t>
+          <t>1047163</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B14-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B14-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139470</t>
+          <t>137746</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181802</t>
+          <t>180709</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99465</t>
+          <t>99764</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137111</t>
+          <t>135969</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>248819</t>
+          <t>251187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>307039</t>
+          <t>306119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,72%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70293</t>
+          <t>70705</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104876</t>
+          <t>104993</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57726</t>
+          <t>58636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88824</t>
+          <t>90774</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140528</t>
+          <t>135714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>187827</t>
+          <t>186502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52629</t>
+          <t>53314</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85894</t>
+          <t>83626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51435</t>
+          <t>50767</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81058</t>
+          <t>79160</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112181</t>
+          <t>112290</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155958</t>
+          <t>155528</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52749</t>
+          <t>55396</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85358</t>
+          <t>86426</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40447</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66760</t>
+          <t>67191</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103876</t>
+          <t>103125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144348</t>
+          <t>143461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29347</t>
+          <t>29824</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54582</t>
+          <t>54258</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27504</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50803</t>
+          <t>48371</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62748</t>
+          <t>62173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95428</t>
+          <t>95216</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116956</t>
+          <t>118269</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155784</t>
+          <t>156203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99369</t>
+          <t>97596</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136863</t>
+          <t>135915</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>225217</t>
+          <t>224534</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279177</t>
+          <t>280582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45592</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72742</t>
+          <t>72992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61883</t>
+          <t>63277</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95021</t>
+          <t>95883</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114092</t>
+          <t>116702</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>156749</t>
+          <t>158872</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56279</t>
+          <t>55339</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87514</t>
+          <t>85703</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44702</t>
+          <t>44287</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74584</t>
+          <t>73079</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>108505</t>
+          <t>106319</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>150240</t>
+          <t>148106</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52552</t>
+          <t>53428</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81973</t>
+          <t>83888</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53876</t>
+          <t>54042</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83829</t>
+          <t>85779</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115223</t>
+          <t>116318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157144</t>
+          <t>159117</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34322</t>
+          <t>33321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58512</t>
+          <t>60373</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38255</t>
+          <t>39872</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65455</t>
+          <t>66041</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78381</t>
+          <t>79896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116265</t>
+          <t>116023</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151139</t>
+          <t>150092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194238</t>
+          <t>192916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47704</t>
+          <t>47745</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74110</t>
+          <t>73858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>206731</t>
+          <t>205468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256815</t>
+          <t>257472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63865</t>
+          <t>62305</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95960</t>
+          <t>95713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20984</t>
+          <t>21150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42063</t>
+          <t>42072</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>90499</t>
+          <t>90726</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130215</t>
+          <t>129097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73412</t>
+          <t>77300</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109072</t>
+          <t>111665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26981</t>
+          <t>27373</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92367</t>
+          <t>92446</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>130690</t>
+          <t>131002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82878</t>
+          <t>83068</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119064</t>
+          <t>120187</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24395</t>
+          <t>24394</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46508</t>
+          <t>45145</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114012</t>
+          <t>115604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>155658</t>
+          <t>156758</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57346</t>
+          <t>58407</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>89230</t>
+          <t>92714</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>13946</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32656</t>
+          <t>32461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76943</t>
+          <t>78554</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115648</t>
+          <t>116587</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>333628</t>
+          <t>330656</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>396471</t>
+          <t>397110</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>230911</t>
+          <t>229668</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>287435</t>
+          <t>284496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>579917</t>
+          <t>580263</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>662089</t>
+          <t>663788</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>160366</t>
+          <t>159918</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>212148</t>
+          <t>210028</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>102351</t>
+          <t>101588</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143055</t>
+          <t>143825</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>269511</t>
+          <t>272435</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>340906</t>
+          <t>336543</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>192448</t>
+          <t>194921</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>247426</t>
+          <t>248047</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>138777</t>
+          <t>140422</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>185603</t>
+          <t>188041</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>349325</t>
+          <t>346203</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>417974</t>
+          <t>418885</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>177965</t>
+          <t>180341</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>230410</t>
+          <t>232335</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>127908</t>
+          <t>126877</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>173434</t>
+          <t>170683</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>319804</t>
+          <t>316186</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>395115</t>
+          <t>385623</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>146611</t>
+          <t>148490</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>196766</t>
+          <t>200127</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>114808</t>
+          <t>115904</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>159213</t>
+          <t>157808</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>277734</t>
+          <t>277130</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>343320</t>
+          <t>342211</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>186433</t>
+          <t>184852</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>235102</t>
+          <t>231537</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>261755</t>
+          <t>259610</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>314141</t>
+          <t>314723</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>459952</t>
+          <t>460217</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>529088</t>
+          <t>532626</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>75267</t>
+          <t>75924</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>110783</t>
+          <t>112329</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>103681</t>
+          <t>103883</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>144276</t>
+          <t>145131</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>190688</t>
+          <t>187998</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>243922</t>
+          <t>241774</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>92085</t>
+          <t>92501</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>130078</t>
+          <t>131754</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100134</t>
+          <t>101780</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>139527</t>
+          <t>142634</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>202978</t>
+          <t>202902</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>260140</t>
+          <t>258975</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>87542</t>
+          <t>89175</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>127715</t>
+          <t>126375</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>90875</t>
+          <t>91546</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>131826</t>
+          <t>130409</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>189563</t>
+          <t>191519</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>242173</t>
+          <t>245226</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>78808</t>
+          <t>80864</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>116931</t>
+          <t>118434</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>79189</t>
+          <t>77054</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>114965</t>
+          <t>113102</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>169707</t>
+          <t>169679</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>220875</t>
+          <t>221937</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>17085</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>35955</t>
+          <t>36859</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>421151</t>
+          <t>420002</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>487245</t>
+          <t>491394</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>446327</t>
+          <t>444598</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>516982</t>
+          <t>521804</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23085</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>44907</t>
+          <t>43995</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>139358</t>
+          <t>136190</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>185810</t>
+          <t>184554</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>170691</t>
+          <t>168020</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>226018</t>
+          <t>221084</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>41952</t>
+          <t>42326</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>69651</t>
+          <t>69471</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>157829</t>
+          <t>156082</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>207498</t>
+          <t>206570</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>209493</t>
+          <t>205956</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>262857</t>
+          <t>264963</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>62929</t>
+          <t>63325</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>94811</t>
+          <t>93229</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>120161</t>
+          <t>121442</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>166204</t>
+          <t>167251</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>193425</t>
+          <t>196311</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>249161</t>
+          <t>249729</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>80980</t>
+          <t>79634</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>114011</t>
+          <t>113127</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>106268</t>
+          <t>105306</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>147979</t>
+          <t>148122</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>193484</t>
+          <t>194343</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>248266</t>
+          <t>249713</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1006585</t>
+          <t>1009992</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1118028</t>
+          <t>1120937</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1237415</t>
+          <t>1232860</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1358142</t>
+          <t>1353566</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2285903</t>
+          <t>2285570</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2446052</t>
+          <t>2446376</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>490228</t>
+          <t>487437</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>575115</t>
+          <t>574157</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>541495</t>
+          <t>544256</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>628135</t>
+          <t>631343</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1054863</t>
+          <t>1052418</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1176987</t>
+          <t>1179798</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>569976</t>
+          <t>563809</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>663326</t>
+          <t>656750</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>560689</t>
+          <t>557116</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>647227</t>
+          <t>647893</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1153502</t>
+          <t>1156138</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1287144</t>
+          <t>1283593</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>579863</t>
+          <t>584379</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>670113</t>
+          <t>671833</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>514585</t>
+          <t>514930</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>605296</t>
+          <t>604183</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1120304</t>
+          <t>1127394</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1253355</t>
+          <t>1254634</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>485077</t>
+          <t>484518</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>569338</t>
+          <t>572595</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>428719</t>
+          <t>429434</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>508256</t>
+          <t>512636</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>931467</t>
+          <t>931579</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1047163</t>
+          <t>1051070</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
